--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487787_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487787_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.101699999999999</v>
+        <v>8.7042</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7248</v>
+        <v>6.0044</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3769</v>
+        <v>2.6998</v>
       </c>
       <c r="G2" t="n">
         <v>2.4149</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4619</v>
+        <v>0.1406</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0463</v>
+        <v>0.3258</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5082</v>
+        <v>-0.1852</v>
       </c>
       <c r="V2" t="n">
         <v>4.9001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5713</v>
+        <v>4.7537</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1041</v>
+        <v>4.1397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4671</v>
+        <v>0.6139</v>
       </c>
       <c r="G3" t="n">
         <v>1.4448</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2285</v>
+        <v>0.4109</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5931</v>
+        <v>0.6287</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3646</v>
+        <v>-0.2178</v>
       </c>
       <c r="V3" t="n">
         <v>1.8574</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2947</v>
+        <v>3.5956</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1439</v>
+        <v>1.6797</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1508</v>
+        <v>1.9159</v>
       </c>
       <c r="G4" t="n">
         <v>2.3136</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0424</v>
+        <v>0.3434</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3171</v>
+        <v>0.2187</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3596</v>
+        <v>0.1247</v>
       </c>
       <c r="V4" t="n">
         <v>0.1061</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3546</v>
+        <v>3.3549</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0353</v>
+        <v>1.065</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3193</v>
+        <v>2.29</v>
       </c>
       <c r="G5" t="n">
         <v>1.1607</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2244</v>
+        <v>0.7759</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7458</v>
+        <v>0.2839</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5214</v>
+        <v>0.492</v>
       </c>
       <c r="V5" t="n">
         <v>2.4589</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9625</v>
+        <v>2.4872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5851</v>
+        <v>0.7575</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3774</v>
+        <v>1.7297</v>
       </c>
       <c r="G6" t="n">
         <v>3.7897</v>
@@ -922,13 +922,13 @@
         <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2871</v>
+        <v>0.2376</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1619</v>
+        <v>0.0105</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1252</v>
+        <v>0.2271</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7076</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.339</v>
+        <v>-0.9257</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5419</v>
+        <v>-0.7623</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8809</v>
+        <v>-0.1635</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.605</v>
+        <v>2.5868</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0149</v>
+        <v>0.6462</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4099</v>
+        <v>1.9406</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.703</v>
+        <v>3.832</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8597</v>
+        <v>1.324</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1568</v>
+        <v>2.508</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0979</v>
+        <v>-1.2452</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8448</v>
+        <v>-0.6778</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2531</v>
+        <v>-0.5674</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-5.2029</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3415</v>
+        <v>1.1098</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2422</v>
+        <v>0.6087</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0993</v>
+        <v>0.5011</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3975</v>
+        <v>-0.4599</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3975</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1958</v>
+        <v>-1.3999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.095</v>
+        <v>-2.8697</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1008</v>
+        <v>1.4698</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5868</v>
+        <v>-0.605</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6462</v>
+        <v>-1.0149</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9406</v>
+        <v>0.4099</v>
       </c>
       <c r="J8" t="n">
-        <v>3.832</v>
+        <v>-1.703</v>
       </c>
       <c r="K8" t="n">
-        <v>1.324</v>
+        <v>-1.8597</v>
       </c>
       <c r="L8" t="n">
-        <v>2.508</v>
+        <v>0.1568</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2452</v>
+        <v>1.0979</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6778</v>
+        <v>0.8448</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5674</v>
+        <v>0.2531</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.2029</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2312</v>
+        <v>0.6027</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4659</v>
+        <v>0.9144</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7653</v>
+        <v>-0.3118</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4599</v>
+        <v>-1.3975</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4599</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8751</v>
+        <v>-2.0304</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5706</v>
+        <v>-2.7553</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6956</v>
+        <v>0.7249</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8663</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1357</v>
+        <v>0.709</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4195</v>
+        <v>0.3958</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2838</v>
+        <v>0.3132</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8196</v>
+        <v>-4.0886</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5258</v>
+        <v>-4.8829</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7062</v>
+        <v>0.7943</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2785</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0843</v>
+        <v>-0.3533</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3667</v>
+        <v>0.2763</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7176</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>14.1249</v>
+        <v>14.451</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0499</v>
+        <v>2.376100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>12.075</v>
+        <v>12.0748</v>
       </c>
       <c r="G11" t="n">
         <v>9.960699999999999</v>
@@ -1282,7 +1282,7 @@
         <v>5.4907</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4699</v>
+        <v>4.469900000000001</v>
       </c>
       <c r="J11" t="n">
         <v>9.860299999999999</v>
@@ -1297,13 +1297,13 @@
         <v>0.1003</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5898999999999999</v>
+        <v>0.5899000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4898000000000001</v>
+        <v>-0.4897999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.243600000000001</v>
+        <v>-6.2436</v>
       </c>
       <c r="Q11" t="n">
         <v>-22.8931</v>
@@ -1312,16 +1312,16 @@
         <v>16.6495</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6502</v>
+        <v>3.9766</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3365</v>
+        <v>3.6628</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3137999999999999</v>
+        <v>0.3138</v>
       </c>
       <c r="V11" t="n">
-        <v>6.757499999999999</v>
+        <v>6.7575</v>
       </c>
       <c r="W11" t="n">
         <v>11.7459</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7149</v>
+        <v>5.3174</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8465</v>
+        <v>3.3823</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.9351</v>
       </c>
       <c r="G12" t="n">
         <v>3.4883</v>
@@ -1390,13 +1390,13 @@
         <v>3.3299</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7191</v>
+        <v>-0.1167</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6714</v>
+        <v>-0.1356</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0477</v>
+        <v>0.019</v>
       </c>
       <c r="V12" t="n">
         <v>0.697</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6493</v>
+        <v>0.9935</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6533</v>
+        <v>-2.155</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3025</v>
+        <v>3.1485</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6743</v>
+        <v>-0.2205</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2733</v>
+        <v>-0.4328</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.401</v>
+        <v>0.2123</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.0944</v>
+        <v>-1.1143</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.118</v>
+        <v>-0.4693</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9765</v>
+        <v>-0.645</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5798</v>
+        <v>0.8938</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1553</v>
+        <v>0.0366</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4245</v>
+        <v>0.8572</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>2.684</v>
+        <v>-0.2936</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9813</v>
+        <v>-0.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7027</v>
+        <v>0.1664</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2335</v>
+        <v>0.467</v>
       </c>
       <c r="W13" t="n">
         <v>0.4599</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6934</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3121</v>
+        <v>0.6732</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5504</v>
+        <v>0.3361</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2384</v>
+        <v>0.337</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1841</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7627</v>
+        <v>-0.4016</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5129</v>
+        <v>-0.7272</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2498</v>
+        <v>0.3256</v>
       </c>
       <c r="V14" t="n">
         <v>1.0508</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0145</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.5836</v>
+        <v>-1.3411</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5691</v>
+        <v>1.4349</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2205</v>
+        <v>1.8774</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4328</v>
+        <v>1.6333</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2123</v>
+        <v>0.2441</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1143</v>
+        <v>1.6287</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4693</v>
+        <v>2.0295</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.645</v>
+        <v>-0.4009</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8938</v>
+        <v>0.2488</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0366</v>
+        <v>-0.3962</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8572</v>
+        <v>0.645</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3016</v>
+        <v>-0.8938</v>
       </c>
       <c r="T15" t="n">
         <v>-0.8885999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4129</v>
+        <v>-0.0052</v>
       </c>
       <c r="V15" t="n">
-        <v>0.467</v>
+        <v>-1.5142</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0071</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3055</v>
+        <v>-0.4189</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3411</v>
+        <v>-0.0029</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0356</v>
+        <v>-0.416</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8774</v>
+        <v>-1.2007</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6333</v>
+        <v>-1.0554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2441</v>
+        <v>-0.1453</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6287</v>
+        <v>0.1261</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0295</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4009</v>
+        <v>0.7446</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2488</v>
+        <v>-1.3268</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3962</v>
+        <v>-0.4369</v>
       </c>
       <c r="O16" t="n">
-        <v>0.645</v>
+        <v>-0.8899</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2931</v>
+        <v>-0.2151</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.129</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4044</v>
+        <v>-0.0861</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5142</v>
+        <v>-0.4599</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5142</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4967</v>
+        <v>-0.5182</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3186</v>
+        <v>-1.7248</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8153</v>
+        <v>1.2066</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2007</v>
+        <v>-3.6743</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0554</v>
+        <v>-2.2733</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1453</v>
+        <v>-1.401</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1261</v>
+        <v>-3.0944</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-2.118</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7446</v>
+        <v>-0.9765</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3268</v>
+        <v>-0.5798</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4369</v>
+        <v>-0.1553</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8899</v>
+        <v>-0.4245</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2929</v>
+        <v>1.5165</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1924</v>
+        <v>0.9097</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4854</v>
+        <v>0.6068</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4599</v>
+        <v>-0.2335</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4599</v>
+        <v>-0.6934</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5455</v>
+        <v>-1.09</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8877</v>
+        <v>-0.7805</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.3095</v>
       </c>
       <c r="G18" t="n">
         <v>0.6175</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8788</v>
+        <v>-0.4233</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4443</v>
+        <v>-0.3372</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4345</v>
+        <v>-0.0861</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2843</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6737</v>
+        <v>-3.776</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1895</v>
+        <v>-3.511</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4843</v>
+        <v>-0.2651</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7246</v>
@@ -1936,13 +1936,13 @@
         <v>3.3299</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0138</v>
+        <v>0.9115</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9407</v>
+        <v>0.6192</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0732</v>
+        <v>0.2924</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1711</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.1936</v>
+        <v>-4.6324</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.547</v>
+        <v>-3.4398</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6467</v>
+        <v>-1.1926</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2964</v>
@@ -2014,13 +2014,13 @@
         <v>3.3299</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1311</v>
+        <v>0.4301</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.7902</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8141</v>
+        <v>-0.3601</v>
       </c>
       <c r="V20" t="n">
         <v>-1.9742</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.5715</v>
+        <v>-6.4809</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5884</v>
+        <v>-2.8383</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9831</v>
+        <v>-3.6426</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6433</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9688</v>
+        <v>0.1218</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7053</v>
+        <v>0.0448</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2635</v>
+        <v>0.077</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3351</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.1247</v>
+        <v>-9.8385</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.0751</v>
+        <v>-12.075</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.05</v>
+        <v>2.2363</v>
       </c>
       <c r="G22" t="n">
         <v>-9.960699999999999</v>
@@ -2143,16 +2143,16 @@
         <v>-4.469899999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1001</v>
+        <v>-0.1001000000000004</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5898999999999994</v>
+        <v>-0.5898999999999992</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4896999999999996</v>
+        <v>0.4897000000000005</v>
       </c>
       <c r="M22" t="n">
-        <v>-9.860399999999998</v>
+        <v>-9.8604</v>
       </c>
       <c r="N22" t="n">
         <v>-4.9008</v>
@@ -2161,7 +2161,7 @@
         <v>-4.9597</v>
       </c>
       <c r="P22" t="n">
-        <v>6.2435</v>
+        <v>6.243500000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-16.6496</v>
@@ -2170,13 +2170,13 @@
         <v>22.893</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.6503</v>
+        <v>0.6357999999999996</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3136999999999998</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.3364</v>
+        <v>0.9497000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-6.7575</v>
